--- a/per-stock/JCI/financials.xlsx
+++ b/per-stock/JCI/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87295336448</v>
+        <v>88356945920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>96145342464</v>
+        <v>97206943744</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.621952</v>
+        <v>44.287464</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.163694</v>
+        <v>25.161451</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5728455</v>
+        <v>3.6162953</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2870374912</v>
+        <v>1366000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>143.08</v>
+        <v>144.82</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D48</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C48</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B48</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B48:E48)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D46</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C46</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B46</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1742,13 +2222,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1758,7 +2238,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1794,11 +2273,6 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>2024-09-30</t>
         </is>
       </c>
@@ -1809,7 +2283,9 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="B2" s="3" t="n">
+        <v>-10431000</v>
+      </c>
       <c r="C2" s="3" t="n">
         <v>-21186000</v>
       </c>
@@ -1822,10 +2298,7 @@
       <c r="F2" s="3" t="n">
         <v>-4368000</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>-5635000</v>
-      </c>
-      <c r="H2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1833,7 +2306,9 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="n">
+        <v>0.171</v>
+      </c>
       <c r="C3" s="3" t="n">
         <v>0.214</v>
       </c>
@@ -1846,10 +2321,7 @@
       <c r="F3" s="3" t="n">
         <v>0.052</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1857,7 +2329,9 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="3" t="n">
+        <v>1028000000</v>
+      </c>
       <c r="C4" s="3" t="n">
         <v>1013000000</v>
       </c>
@@ -1870,10 +2344,7 @@
       <c r="F4" s="3" t="n">
         <v>843000000</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>717000000</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1881,7 +2352,9 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="3" t="n">
+        <v>-61000000</v>
+      </c>
       <c r="C5" s="3" t="n">
         <v>-99000000</v>
       </c>
@@ -1894,10 +2367,7 @@
       <c r="F5" s="3" t="n">
         <v>-84000000</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>-49000000</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1905,7 +2375,9 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="3" t="n">
+        <v>-61000000</v>
+      </c>
       <c r="C6" s="3" t="n">
         <v>-99000000</v>
       </c>
@@ -1918,10 +2390,7 @@
       <c r="F6" s="3" t="n">
         <v>-84000000</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>-49000000</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1929,7 +2398,9 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
+      <c r="B7" s="3" t="n">
+        <v>609000000</v>
+      </c>
       <c r="C7" s="3" t="n">
         <v>555000000</v>
       </c>
@@ -1942,10 +2413,7 @@
       <c r="F7" s="3" t="n">
         <v>427000000</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>329000000</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1953,7 +2421,9 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
+      <c r="B8" s="3" t="n">
+        <v>169000000</v>
+      </c>
       <c r="C8" s="3" t="n">
         <v>164000000</v>
       </c>
@@ -1966,10 +2436,7 @@
       <c r="F8" s="3" t="n">
         <v>202000000</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>193000000</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1977,7 +2444,9 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
+      <c r="B9" s="3" t="n">
+        <v>3880000000</v>
+      </c>
       <c r="C9" s="3" t="n">
         <v>3723000000</v>
       </c>
@@ -1990,10 +2459,7 @@
       <c r="F9" s="3" t="n">
         <v>3607000000</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>3500000000</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2001,7 +2467,9 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
+      <c r="B10" s="3" t="n">
+        <v>967000000</v>
+      </c>
       <c r="C10" s="3" t="n">
         <v>914000000</v>
       </c>
@@ -2014,10 +2482,7 @@
       <c r="F10" s="3" t="n">
         <v>759000000</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>668000000</v>
-      </c>
-      <c r="H10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2025,7 +2490,9 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="3" t="n">
+        <v>798000000</v>
+      </c>
       <c r="C11" s="3" t="n">
         <v>750000000</v>
       </c>
@@ -2038,10 +2505,7 @@
       <c r="F11" s="3" t="n">
         <v>557000000</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>475000000</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2049,7 +2513,9 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="3" t="n">
+        <v>-63000000</v>
+      </c>
       <c r="C12" s="3" t="n">
         <v>-47000000</v>
       </c>
@@ -2062,10 +2528,7 @@
       <c r="F12" s="3" t="n">
         <v>-58000000</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>-70000000</v>
-      </c>
-      <c r="H12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2073,7 +2536,9 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>60000000</v>
+      </c>
       <c r="C13" s="3" t="n">
         <v>42000000</v>
       </c>
@@ -2086,10 +2551,7 @@
       <c r="F13" s="3" t="n">
         <v>56000000</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>67000000</v>
-      </c>
-      <c r="H13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2097,7 +2559,9 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="C14" s="3" t="n">
         <v>2000000</v>
       </c>
@@ -2110,10 +2574,7 @@
       <c r="F14" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="H14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2121,7 +2582,9 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="n">
+        <v>659569000</v>
+      </c>
       <c r="C15" s="3" t="n">
         <v>632814000</v>
       </c>
@@ -2134,10 +2597,7 @@
       <c r="F15" s="3" t="n">
         <v>506632000</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>372365000</v>
-      </c>
-      <c r="H15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2145,7 +2605,9 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="3" t="n">
+        <v>613000000</v>
+      </c>
       <c r="C16" s="3" t="n">
         <v>524000000</v>
       </c>
@@ -2158,10 +2620,7 @@
       <c r="F16" s="3" t="n">
         <v>478000000</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>419000000</v>
-      </c>
-      <c r="H16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2169,7 +2628,9 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="n">
+        <v>5281000000</v>
+      </c>
       <c r="C17" s="3" t="n">
         <v>4944000000</v>
       </c>
@@ -2182,10 +2643,7 @@
       <c r="F17" s="3" t="n">
         <v>5034000000</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>4899000000</v>
-      </c>
-      <c r="H17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2209,7 +2667,6 @@
         <v>661000000</v>
       </c>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2233,7 +2690,6 @@
         <v>659100000</v>
       </c>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2257,7 +2713,6 @@
         <v>0.72</v>
       </c>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2281,7 +2736,6 @@
         <v>0.73</v>
       </c>
       <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2289,7 +2743,9 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
+      <c r="B22" s="3" t="n">
+        <v>613000000</v>
+      </c>
       <c r="C22" s="3" t="n">
         <v>524000000</v>
       </c>
@@ -2302,10 +2758,7 @@
       <c r="F22" s="3" t="n">
         <v>478000000</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>419000000</v>
-      </c>
-      <c r="H22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2313,7 +2766,9 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>613000000</v>
+      </c>
       <c r="C23" s="3" t="n">
         <v>524000000</v>
       </c>
@@ -2326,10 +2781,7 @@
       <c r="F23" s="3" t="n">
         <v>478000000</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>419000000</v>
-      </c>
-      <c r="H23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2337,7 +2789,9 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
+      <c r="B24" s="3" t="n">
+        <v>613000000</v>
+      </c>
       <c r="C24" s="3" t="n">
         <v>524000000</v>
       </c>
@@ -2350,10 +2804,7 @@
       <c r="F24" s="3" t="n">
         <v>478000000</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>419000000</v>
-      </c>
-      <c r="H24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2361,7 +2812,9 @@
           <t>Minority Interests</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
+      <c r="B25" s="3" t="n">
+        <v>-3000000</v>
+      </c>
       <c r="C25" s="3" t="n">
         <v>-1000000</v>
       </c>
@@ -2374,10 +2827,7 @@
       <c r="F25" s="3" t="n">
         <v>-48000000</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>-32000000</v>
-      </c>
-      <c r="H25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2385,7 +2835,9 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
+      <c r="B26" s="3" t="n">
+        <v>616000000</v>
+      </c>
       <c r="C26" s="3" t="n">
         <v>525000000</v>
       </c>
@@ -2398,10 +2850,7 @@
       <c r="F26" s="3" t="n">
         <v>526000000</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>451000000</v>
-      </c>
-      <c r="H26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2409,7 +2858,9 @@
           <t>Net Income Discontinuous Operations</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="C27" s="3" t="n">
         <v>-31000000</v>
       </c>
@@ -2422,10 +2873,7 @@
       <c r="F27" s="3" t="n">
         <v>51000000</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2433,7 +2881,9 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
+      <c r="B28" s="3" t="n">
+        <v>612000000</v>
+      </c>
       <c r="C28" s="3" t="n">
         <v>556000000</v>
       </c>
@@ -2446,10 +2896,7 @@
       <c r="F28" s="3" t="n">
         <v>475000000</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>361000000</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2457,7 +2904,9 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
+      <c r="B29" s="3" t="n">
+        <v>126000000</v>
+      </c>
       <c r="C29" s="3" t="n">
         <v>152000000</v>
       </c>
@@ -2470,10 +2919,7 @@
       <c r="F29" s="3" t="n">
         <v>26000000</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>47000000</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2481,7 +2927,9 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
+      <c r="B30" s="3" t="n">
+        <v>738000000</v>
+      </c>
       <c r="C30" s="3" t="n">
         <v>708000000</v>
       </c>
@@ -2494,10 +2942,7 @@
       <c r="F30" s="3" t="n">
         <v>501000000</v>
       </c>
-      <c r="G30" s="3" t="n">
-        <v>408000000</v>
-      </c>
-      <c r="H30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2505,7 +2950,9 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
+      <c r="B31" s="3" t="n">
+        <v>-60000000</v>
+      </c>
       <c r="C31" s="3" t="n">
         <v>-98000000</v>
       </c>
@@ -2518,10 +2965,7 @@
       <c r="F31" s="3" t="n">
         <v>-83000000</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>-49000000</v>
-      </c>
-      <c r="H31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2529,7 +2973,9 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
+      <c r="B32" s="3" t="n">
+        <v>-57000000</v>
+      </c>
       <c r="C32" s="3" t="n">
         <v>-87000000</v>
       </c>
@@ -2542,10 +2988,7 @@
       <c r="F32" s="3" t="n">
         <v>-62000000</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>-33000000</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2558,8 +3001,7 @@
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n">
+      <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2569,7 +3011,9 @@
           <t>Write Off</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
+      <c r="B34" s="3" t="n">
+        <v>21000000</v>
+      </c>
       <c r="C34" s="3" t="n">
         <v>50000000</v>
       </c>
@@ -2579,9 +3023,10 @@
       <c r="E34" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="F34" s="3" t="n"/>
+      <c r="F34" s="3" t="n">
+        <v>40000000</v>
+      </c>
       <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2589,7 +3034,9 @@
           <t>Impairment Of Capital Assets</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
+      <c r="B35" s="3" t="n">
+        <v>36000000</v>
+      </c>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n">
         <v>360000000</v>
@@ -2601,7 +3048,6 @@
         <v>22000000</v>
       </c>
       <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2609,7 +3055,9 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
+      <c r="B36" s="3" t="n">
+        <v>36000000</v>
+      </c>
       <c r="C36" s="3" t="n">
         <v>37000000</v>
       </c>
@@ -2620,12 +3068,9 @@
         <v>49000000</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
+        <v>22000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2633,7 +3078,9 @@
           <t>Earnings From Equity Interest</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
+      <c r="B37" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="C37" s="3" t="n">
         <v>1000000</v>
       </c>
@@ -2646,10 +3093,7 @@
       <c r="F37" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2657,7 +3101,9 @@
           <t>Gain On Sale Of Security</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
+      <c r="B38" s="3" t="n">
+        <v>-4000000</v>
+      </c>
       <c r="C38" s="3" t="n">
         <v>-12000000</v>
       </c>
@@ -2670,10 +3116,7 @@
       <c r="F38" s="3" t="n">
         <v>-22000000</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>-16000000</v>
-      </c>
-      <c r="H38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2681,7 +3124,9 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
+      <c r="B39" s="3" t="n">
+        <v>-63000000</v>
+      </c>
       <c r="C39" s="3" t="n">
         <v>-47000000</v>
       </c>
@@ -2694,10 +3139,7 @@
       <c r="F39" s="3" t="n">
         <v>-58000000</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>-70000000</v>
-      </c>
-      <c r="H39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2705,7 +3147,9 @@
           <t>Total Other Finance Cost</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
+      <c r="B40" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="C40" s="3" t="n">
         <v>7000000</v>
       </c>
@@ -2718,10 +3162,7 @@
       <c r="F40" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="H40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2729,7 +3170,9 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
+      <c r="B41" s="3" t="n">
+        <v>60000000</v>
+      </c>
       <c r="C41" s="3" t="n">
         <v>42000000</v>
       </c>
@@ -2742,10 +3185,7 @@
       <c r="F41" s="3" t="n">
         <v>56000000</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>67000000</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2753,7 +3193,9 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
+      <c r="B42" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="C42" s="3" t="n">
         <v>2000000</v>
       </c>
@@ -2766,10 +3208,7 @@
       <c r="F42" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2777,7 +3216,9 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n"/>
+      <c r="B43" s="3" t="n">
+        <v>861000000</v>
+      </c>
       <c r="C43" s="3" t="n">
         <v>853000000</v>
       </c>
@@ -2790,10 +3231,7 @@
       <c r="F43" s="3" t="n">
         <v>642000000</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>527000000</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2801,7 +3239,9 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
+      <c r="B44" s="3" t="n">
+        <v>1401000000</v>
+      </c>
       <c r="C44" s="3" t="n">
         <v>1221000000</v>
       </c>
@@ -2814,10 +3254,7 @@
       <c r="F44" s="3" t="n">
         <v>1427000000</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>1399000000</v>
-      </c>
-      <c r="H44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2825,7 +3262,9 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
+      <c r="B45" s="3" t="n">
+        <v>1401000000</v>
+      </c>
       <c r="C45" s="3" t="n">
         <v>1221000000</v>
       </c>
@@ -2838,10 +3277,7 @@
       <c r="F45" s="3" t="n">
         <v>1427000000</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>1399000000</v>
-      </c>
-      <c r="H45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2849,7 +3285,9 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n"/>
+      <c r="B46" s="3" t="n">
+        <v>2262000000</v>
+      </c>
       <c r="C46" s="3" t="n">
         <v>2074000000</v>
       </c>
@@ -2862,10 +3300,7 @@
       <c r="F46" s="3" t="n">
         <v>2069000000</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>1926000000</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2873,7 +3308,9 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n"/>
+      <c r="B47" s="3" t="n">
+        <v>3880000000</v>
+      </c>
       <c r="C47" s="3" t="n">
         <v>3723000000</v>
       </c>
@@ -2886,10 +3323,7 @@
       <c r="F47" s="3" t="n">
         <v>3607000000</v>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>3500000000</v>
-      </c>
-      <c r="H47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2897,7 +3331,9 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
+      <c r="B48" s="3" t="n">
+        <v>6142000000</v>
+      </c>
       <c r="C48" s="3" t="n">
         <v>5797000000</v>
       </c>
@@ -2910,10 +3346,7 @@
       <c r="F48" s="3" t="n">
         <v>5676000000</v>
       </c>
-      <c r="G48" s="3" t="n">
-        <v>5426000000</v>
-      </c>
-      <c r="H48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2921,7 +3354,9 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n"/>
+      <c r="B49" s="3" t="n">
+        <v>6142000000</v>
+      </c>
       <c r="C49" s="3" t="n">
         <v>5797000000</v>
       </c>
@@ -2934,17 +3369,14 @@
       <c r="F49" s="3" t="n">
         <v>5676000000</v>
       </c>
-      <c r="G49" s="3" t="n">
-        <v>5426000000</v>
-      </c>
-      <c r="H49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4448,7 +4880,1635 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>30501903</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>30501903</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>30501903</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>30086539</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>30086539</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>610115603</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>612004462</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>611130391</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>654385440</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>658047305</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>640617506</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>642506365</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>641632294</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>684471979</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>688133844</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8825000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>9153000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>9501000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>9562000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>9191000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>9523000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>9705000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9880000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>10293000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>9986000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-6513000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-6956000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-7319000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-4735000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-4587000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>23041000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>22909000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>22807000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>26123000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>25791000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>386000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-60000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-779000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-501000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-467000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-6513000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-6956000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-7319000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-4735000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-4587000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>13518000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>13204000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>12927000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>15830000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>15805000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>22131000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>21905000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>21518000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>24276000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>23972000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>13543000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>13233000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>12954000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>17045000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>17032000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1215000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1227000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>13518000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>13204000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>12927000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>15830000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>15805000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-494000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-631000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-642000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-1281000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-1128000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-494000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-631000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-642000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-1281000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-1128000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1362000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1351000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1302000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1301000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1299000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>278000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>746000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>599000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>15368000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>14902000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>14865000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>17659000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>17626000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>24811000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>24750000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>24985000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>26348000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>25335000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>14206000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>14249000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>14044000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>13998000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>13518000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5380000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5333000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>5233000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>4975000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>4741000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Liabilities Heldfor Sale Non Current</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>398000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>429000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>201000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>179000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>201000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>179000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>8613000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>8701000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>8591000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>8446000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>8167000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>8613000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>8701000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>8591000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>8446000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>8167000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>10605000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>10501000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>10941000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>12350000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>11817000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>2418000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>2450000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2300000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3584000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>3532000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2845000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2542000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>2470000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2428000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2380000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2845000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>2542000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2470000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>2428000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2380000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>910000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1004000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1289000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1847000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1819000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>910000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1004000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1289000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1847000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1819000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>568000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>566000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>570000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>558000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>441000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>236000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>323000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>627000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>588000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Commercial Paper</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>441000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>673000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>822000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>891000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1268000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1070000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>832000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>3610000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3614000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>3614000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>3421000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>3254000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>3610000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>3614000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3614000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>3421000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>3254000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>3610000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3614000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3614000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>3421000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>3254000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>38354000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>37983000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>37939000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>43393000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>42367000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>27363000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>27542000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>27777000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>31544000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>31017000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>5236000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>5252000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>5338000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>8524000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>8203000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>20031000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>20160000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>20246000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>20565000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>20392000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>3484000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>3550000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>3613000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>3856000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>3883000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>16547000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>16610000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>16633000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>16709000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>16509000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>2096000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2130000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2193000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2455000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2422000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="3" t="n">
+        <v>-3917000000</v>
+      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>-3443000000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>6110000000</v>
+      </c>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>5846000000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>382000000</v>
+      </c>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>418000000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>4586000000</v>
+      </c>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
+        <v>4347000000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>1095000000</v>
+      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>1033000000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>48000000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>10991000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>10441000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>10162000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>11849000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>11350000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1725000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1747000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>1680000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>1145000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>1085000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1993000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1856000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1933000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1932000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1820000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1829000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1756000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>982000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>997000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>972000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>941000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>910000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>135000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>132000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>142000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>128000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>816000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>797000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>716000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>746000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>718000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>6614000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>6190000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>6269000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>6151000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>5858000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>6614000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>6190000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>6269000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>6151000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>5858000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>-172000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>-177000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>-205000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-231000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>-233000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>6786000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>6367000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>6474000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>6382000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>6091000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>698000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>552000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>379000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>731000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>795000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>698000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>552000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>379000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>731000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>795000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5722,13 +7782,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5738,6 +7798,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5748,30 +7809,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5784,21 +7850,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>573000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>464000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-572000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>901000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>505000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>131000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5807,21 +7874,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-215000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-5021000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-310000000</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>-330000000</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-330000000</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5830,21 +7898,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-352000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-287000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-1146000000</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E4" s="3" t="n">
-        <v>92000000</v>
+        <v>594000000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-594000000</v>
+        <v>-502000000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5853,21 +7922,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>265000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>116000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>707000000</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>-75000000</v>
-      </c>
       <c r="E5" s="3" t="n">
-        <v>-248000000</v>
+        <v>-669000000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1381000000</v>
+        <v>346000000</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5876,21 +7946,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-68000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-80000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-130000000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>-94000000</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>-94000000</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-116000000</v>
+        <v>-94000000</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5899,21 +7970,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>698000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>552000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>379000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>731000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>795000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>1237000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5922,21 +7994,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>6000000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>-2000000</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>-2000000</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-21000000</v>
+        <v>-2000000</v>
       </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5945,21 +8018,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>552000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>398000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>731000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>795000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>1237000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>767000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5968,21 +8042,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-43000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-201000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-169000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>154000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5991,21 +8066,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>170000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-315000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>139000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-271000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>337000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6014,21 +8090,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-258000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>4000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6037,21 +8114,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-566000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-464000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-6103000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-746000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-740000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>201000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6060,19 +8138,20 @@
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
         <v>-430000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-109000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-65000000</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="G14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6081,21 +8160,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-566000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-464000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-5673000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-637000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-675000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>201000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6104,21 +8184,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-20000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-48000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>101000000</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>-13000000</v>
-      </c>
       <c r="E16" s="3" t="n">
-        <v>-49000000</v>
+        <v>-118000000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-11000000</v>
+        <v>56000000</v>
       </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6128,12 +8209,13 @@
       </c>
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6142,21 +8224,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-244000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-245000000</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>-243000000</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>-243000000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-245000000</v>
+        <v>-243000000</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>-245000000</v>
       </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6165,19 +8248,20 @@
         </is>
       </c>
       <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
-        <v>-243000000</v>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n">
         <v>-243000000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-245000000</v>
+        <v>-243000000</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>-245000000</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>-245000000</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>-247000000</v>
       </c>
     </row>
@@ -6188,21 +8272,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-215000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-5021000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-310000000</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-330000000</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-330000000</v>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6211,21 +8296,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-215000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-5021000000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-310000000</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-330000000</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>-330000000</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6234,21 +8320,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-87000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-171000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-401000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-75000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-156000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>787000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6257,21 +8344,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>251000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-186000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-245000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-75000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>346000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>12000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6279,14 +8367,15 @@
           <t>Short Term Debt Payments</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n">
         <v>-186000000</v>
       </c>
-      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6296,16 +8385,17 @@
       </c>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n">
         <v>-75000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>346000000</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="G25" s="3" t="n">
         <v>12000000</v>
       </c>
-      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6314,21 +8404,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-338000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>15000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-156000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-502000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>775000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6337,21 +8428,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-538000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-101000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-1146000000</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E27" s="3" t="n">
-        <v>92000000</v>
+        <v>594000000</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-594000000</v>
+        <v>-502000000</v>
       </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6360,21 +8452,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>116000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>990000000</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>-594000000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1369000000</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6383,21 +8476,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-49000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>90000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>6488000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-110000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-129000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-115000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6409,18 +8503,19 @@
         <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
         <v>6598000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-25000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-17000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-10000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6429,21 +8524,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-49000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>90000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-110000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-85000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-112000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-105000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6452,21 +8548,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-12000000</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>9000000</v>
-      </c>
       <c r="E32" s="3" t="n">
-        <v>-18000000</v>
+        <v>10000000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>11000000</v>
+        <v>-19000000</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6475,15 +8572,20 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="H33" s="3" t="n">
         <v>341000000</v>
       </c>
     </row>
@@ -6494,15 +8596,20 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>344000000</v>
       </c>
     </row>
@@ -6513,21 +8620,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-68000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-80000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-130000000</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>-94000000</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>-94000000</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-116000000</v>
+        <v>-94000000</v>
       </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6536,21 +8644,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>641000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>544000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-442000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>995000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>599000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>247000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6559,21 +8668,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-31000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-67000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-1410000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>208000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>49000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-2000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6582,21 +8692,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>672000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>611000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>968000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>787000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>550000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>249000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6605,21 +8716,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-172000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-143000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-302000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-14000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-133000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-279000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6628,21 +8740,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-23000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>2000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6651,21 +8764,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>88000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-292000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-76000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-42000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-171000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6674,21 +8788,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>119000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>281000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>117000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-379000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6697,21 +8812,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>119000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>281000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>117000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>-379000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6720,21 +8836,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>238000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-175000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>663000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>258000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>180000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-407000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6743,21 +8860,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>92000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-12000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-544000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>23000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>-63000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>28000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6766,21 +8884,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>92000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-12000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-544000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>23000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-63000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>28000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6789,21 +8908,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-28000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-112000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-52000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>-12000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>-15000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6812,21 +8932,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>-460000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>71000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>-132000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>-172000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>-191000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>284000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6835,21 +8956,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-460000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>71000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-132000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-172000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>-191000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>284000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6858,21 +8980,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>61000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>306000000</v>
       </c>
-      <c r="D50" s="3" t="n">
-        <v>-1000000</v>
-      </c>
       <c r="E50" s="3" t="n">
-        <v>49000000</v>
+        <v>5000000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>16000000</v>
+        <v>43000000</v>
       </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6881,21 +9004,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>33000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>48000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>28000000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6904,21 +9028,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>-18000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>21000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>341000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>-39000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>-53000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>-54000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6927,21 +9052,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>-18000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>21000000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>341000000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>-39000000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>-53000000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>-54000000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6950,21 +9076,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>169000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>164000000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>280000000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>190000000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>202000000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>193000000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6973,21 +9100,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>169000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>164000000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>280000000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>190000000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>202000000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>193000000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6996,21 +9124,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>-19000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>-82000000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>40000000</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>-15000000</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>-21000000</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-16000000</v>
+        <v>-15000000</v>
       </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7019,21 +9148,22 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>-12000000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>42000000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>-16000000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7046,7 +9176,8 @@
       <c r="D58" s="3" t="n"/>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n">
         <v>42000000</v>
       </c>
     </row>
@@ -7057,15 +9188,20 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>-70000000</v>
       </c>
-      <c r="C59" s="3" t="n"/>
       <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7074,28 +9210,29 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
+        <v>612000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>556000000</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>270000000</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>618000000</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>475000000</v>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>361000000</v>
-      </c>
       <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
